--- a/artfynd/A 34681-2021 artfynd.xlsx
+++ b/artfynd/A 34681-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34681-2021 artfynd.xlsx
+++ b/artfynd/A 34681-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16446385</v>
+        <v>16501822</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519191.3396231859</v>
+        <v>519191</v>
       </c>
       <c r="R2" t="n">
-        <v>7265880.237635578</v>
+        <v>7265852</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-07-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2014-07-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,53 +766,60 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Rönnbäck</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16446388</v>
+        <v>16558245</v>
       </c>
       <c r="B3" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519189.4202140668</v>
+        <v>519191</v>
       </c>
       <c r="R3" t="n">
-        <v>7266045.381571727</v>
+        <v>7265880</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +862,9 @@
           <t>2014-07-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-07-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +891,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16446413</v>
+        <v>16558270</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519191.3396231859</v>
+        <v>519191</v>
       </c>
       <c r="R4" t="n">
-        <v>7265880.237635578</v>
+        <v>7265880</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,19 +959,9 @@
           <t>2014-07-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-07-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16501857</v>
+        <v>16501720</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519232.4587964254</v>
+        <v>519140</v>
       </c>
       <c r="R5" t="n">
-        <v>7265944.829854785</v>
+        <v>7265971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1058,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1068,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,11 +1081,11 @@
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2 substratenheter</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1135,55 +1107,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16501688</v>
+        <v>16558204</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rönnbäcksnäset, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519137.7568396605</v>
+        <v>519189</v>
       </c>
       <c r="R6" t="n">
-        <v>7265941.716006457</v>
+        <v>7266045</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,22 +1172,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:12</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:12</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,53 +1192,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Rönnbäck</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16501769</v>
+        <v>16558225</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,13 +1239,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519194.0483735272</v>
+        <v>519191</v>
       </c>
       <c r="R7" t="n">
-        <v>7265847.472041594</v>
+        <v>7265880</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,22 +1269,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,43 +1285,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Rönnbäck</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16501720</v>
+        <v>16501690</v>
       </c>
       <c r="B8" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519140.4739042301</v>
+        <v>519202</v>
       </c>
       <c r="R8" t="n">
-        <v>7265970.781566513</v>
+        <v>7265860</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1371,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1381,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,37 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16501845</v>
+        <v>16501807</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>1506</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519257.85224776</v>
+        <v>519191</v>
       </c>
       <c r="R9" t="n">
-        <v>7265937.113286388</v>
+        <v>7265852</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,37 +1539,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16501807</v>
+        <v>16558285</v>
       </c>
       <c r="B10" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1506</v>
+        <v>1588</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1665,13 +1574,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519190.6919918755</v>
+        <v>519191</v>
       </c>
       <c r="R10" t="n">
-        <v>7265852.429705577</v>
+        <v>7265880</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1695,22 +1604,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,65 +1620,48 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Rönnbäck</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16501842</v>
+        <v>16558202</v>
       </c>
       <c r="B11" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92283</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1789,13 +1671,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519287.0094753712</v>
+        <v>519120</v>
       </c>
       <c r="R11" t="n">
-        <v>7265925.687103828</v>
+        <v>7266008</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1819,22 +1701,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,65 +1717,48 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Rönnbäck</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16501885</v>
+        <v>16501842</v>
       </c>
       <c r="B12" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1913,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519257.85224776</v>
+        <v>519287</v>
       </c>
       <c r="R12" t="n">
-        <v>7265937.113286388</v>
+        <v>7265926</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,7 +1803,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1958,7 +1813,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1997,15 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16501767</v>
+        <v>16501843</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2037,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519174.0824818183</v>
+        <v>519129</v>
       </c>
       <c r="R13" t="n">
-        <v>7265914.151937218</v>
+        <v>7265954</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2072,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2082,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2121,37 +1971,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16501887</v>
+        <v>16501845</v>
       </c>
       <c r="B14" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2161,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519129.0159962648</v>
+        <v>519258</v>
       </c>
       <c r="R14" t="n">
-        <v>7265754.501463166</v>
+        <v>7265937</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2196,7 +2041,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2206,7 +2051,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2245,15 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16501843</v>
+        <v>16501846</v>
       </c>
       <c r="B15" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,10 +2125,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519128.5382827088</v>
+        <v>519131</v>
       </c>
       <c r="R15" t="n">
-        <v>7265953.68950721</v>
+        <v>7265930</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2320,7 +2160,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2330,7 +2170,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,37 +2209,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16501886</v>
+        <v>16501852</v>
       </c>
       <c r="B16" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2409,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519130.7735718585</v>
+        <v>519251</v>
       </c>
       <c r="R16" t="n">
-        <v>7265929.635981414</v>
+        <v>7265960</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2444,7 +2279,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2454,7 +2289,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2493,37 +2328,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16501633</v>
+        <v>16501857</v>
       </c>
       <c r="B17" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2533,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519130.7735718585</v>
+        <v>519232</v>
       </c>
       <c r="R17" t="n">
-        <v>7265929.635981414</v>
+        <v>7265945</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2568,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2578,7 +2408,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2591,11 +2421,11 @@
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>2 substratenheter</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2617,37 +2447,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16501883</v>
+        <v>16558436</v>
       </c>
       <c r="B18" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2657,13 +2482,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519128.5382827088</v>
+        <v>519365</v>
       </c>
       <c r="R18" t="n">
-        <v>7265953.68950721</v>
+        <v>7265878</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2687,22 +2512,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2713,43 +2528,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Rönnbäck</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16501846</v>
+        <v>16558437</v>
       </c>
       <c r="B19" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,13 +2579,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519130.7735718585</v>
+        <v>519191</v>
       </c>
       <c r="R19" t="n">
-        <v>7265929.635981414</v>
+        <v>7265880</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2811,22 +2609,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,43 +2625,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Rönnbäck</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16501736</v>
+        <v>16558439</v>
       </c>
       <c r="B20" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2881,21 +2652,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2905,13 +2676,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519190.6919918755</v>
+        <v>519059</v>
       </c>
       <c r="R20" t="n">
-        <v>7265852.429705577</v>
+        <v>7265994</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2935,22 +2706,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2961,43 +2722,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Rönnbäck</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16501822</v>
+        <v>16558440</v>
       </c>
       <c r="B21" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,21 +2749,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3029,13 +2773,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519190.6919918755</v>
+        <v>519288</v>
       </c>
       <c r="R21" t="n">
-        <v>7265852.429705577</v>
+        <v>7266034</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3059,22 +2803,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,78 +2819,63 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Rönnbäck</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16501765</v>
+        <v>16501688</v>
       </c>
       <c r="B22" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rönnbäcksnäset, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519182.0085637427</v>
+        <v>519138</v>
       </c>
       <c r="R22" t="n">
-        <v>7265909.224463314</v>
+        <v>7265942</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3188,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3198,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3209,14 +2928,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3237,50 +2948,47 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16501690</v>
+        <v>16501694</v>
       </c>
       <c r="B23" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rönnbäcksnäset, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519201.8624665141</v>
+        <v>519195</v>
       </c>
       <c r="R23" t="n">
-        <v>7265859.558038571</v>
+        <v>7265867</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3312,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3322,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3333,14 +3041,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3361,37 +3061,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>16501632</v>
+        <v>16558444</v>
       </c>
       <c r="B24" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3401,13 +3096,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519257.85224776</v>
+        <v>519059</v>
       </c>
       <c r="R24" t="n">
-        <v>7265937.113286388</v>
+        <v>7265994</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3431,22 +3126,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2014-07-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3457,65 +3142,48 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Rönnbäck</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16501852</v>
+        <v>16501883</v>
       </c>
       <c r="B25" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3525,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519251.4671120214</v>
+        <v>519129</v>
       </c>
       <c r="R25" t="n">
-        <v>7265960.309291778</v>
+        <v>7265954</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3560,7 +3228,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3570,7 +3238,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3609,52 +3277,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>16501694</v>
+        <v>16501885</v>
       </c>
       <c r="B26" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rönnbäcksnäset, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519194.7479517282</v>
+        <v>519258</v>
       </c>
       <c r="R26" t="n">
-        <v>7265867.395755494</v>
+        <v>7265937</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3686,7 +3347,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3696,7 +3357,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3707,6 +3368,14 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3727,37 +3396,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>16558199</v>
+        <v>16501886</v>
       </c>
       <c r="B27" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3767,13 +3431,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519191.3396231859</v>
+        <v>519131</v>
       </c>
       <c r="R27" t="n">
-        <v>7265880.237635578</v>
+        <v>7265930</v>
       </c>
       <c r="S27" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3797,22 +3461,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-07-10</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2014-07-10</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3823,53 +3487,60 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Rönnbäck</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>16558437</v>
+        <v>16501887</v>
       </c>
       <c r="B28" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3879,13 +3550,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519191.3396231859</v>
+        <v>519129</v>
       </c>
       <c r="R28" t="n">
-        <v>7265880.237635578</v>
+        <v>7265755</v>
       </c>
       <c r="S28" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3909,22 +3580,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-07-10</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2014-07-10</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3935,31 +3606,38 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Rönnbäck</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>16558465</v>
       </c>
       <c r="B29" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3991,13 +3669,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519239.5787100368</v>
+        <v>519240</v>
       </c>
       <c r="R29" t="n">
-        <v>7265936.162534627</v>
+        <v>7265936</v>
       </c>
       <c r="S29" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4024,19 +3702,9 @@
           <t>2014-07-07</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2014-07-11</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4063,37 +3731,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16558204</v>
+        <v>16558466</v>
       </c>
       <c r="B30" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4103,13 +3766,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519189.4202140668</v>
+        <v>519152</v>
       </c>
       <c r="R30" t="n">
-        <v>7266045.381571727</v>
+        <v>7265825</v>
       </c>
       <c r="S30" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4136,19 +3799,9 @@
           <t>2014-07-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2014-07-11</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4175,37 +3828,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>16558270</v>
+        <v>16558469</v>
       </c>
       <c r="B31" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4215,13 +3863,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519191.3396231859</v>
+        <v>519288</v>
       </c>
       <c r="R31" t="n">
-        <v>7265880.237635578</v>
+        <v>7266034</v>
       </c>
       <c r="S31" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4248,19 +3896,9 @@
           <t>2014-07-07</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2014-07-11</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4287,37 +3925,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>16558285</v>
+        <v>16501632</v>
       </c>
       <c r="B32" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1588</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4327,13 +3960,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519191.3396231859</v>
+        <v>519258</v>
       </c>
       <c r="R32" t="n">
-        <v>7265880.237635578</v>
+        <v>7265937</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4357,22 +3990,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-07-10</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2014-07-10</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4383,53 +4016,60 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Rönnbäck</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16558245</v>
+        <v>16501633</v>
       </c>
       <c r="B33" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4439,13 +4079,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519191.3396231859</v>
+        <v>519131</v>
       </c>
       <c r="R33" t="n">
-        <v>7265880.237635578</v>
+        <v>7265930</v>
       </c>
       <c r="S33" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4469,22 +4109,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-07-10</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2014-07-10</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4495,53 +4135,60 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Rönnbäck</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16558200</v>
+        <v>16446385</v>
       </c>
       <c r="B34" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4551,13 +4198,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519152.2358157501</v>
+        <v>519191</v>
       </c>
       <c r="R34" t="n">
-        <v>7265824.787552924</v>
+        <v>7265880</v>
       </c>
       <c r="S34" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4584,19 +4231,9 @@
           <t>2014-07-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2014-07-11</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4623,37 +4260,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16558198</v>
+        <v>16446388</v>
       </c>
       <c r="B35" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4663,13 +4295,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519219.6406917829</v>
+        <v>519189</v>
       </c>
       <c r="R35" t="n">
-        <v>7265935.615879476</v>
+        <v>7266045</v>
       </c>
       <c r="S35" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4696,19 +4328,9 @@
           <t>2014-07-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2014-07-11</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4735,37 +4357,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>16558225</v>
+        <v>16446413</v>
       </c>
       <c r="B36" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4775,13 +4392,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519191.3396231859</v>
+        <v>519191</v>
       </c>
       <c r="R36" t="n">
-        <v>7265880.237635578</v>
+        <v>7265880</v>
       </c>
       <c r="S36" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4808,19 +4425,9 @@
           <t>2014-07-07</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2014-07-11</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4844,118 +4451,6 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>16558466</v>
-      </c>
-      <c r="B37" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Rönnbäcksnäset, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>519152.2358157501</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7265824.787552924</v>
-      </c>
-      <c r="S37" t="n">
-        <v>100</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2014-07-07</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2014-07-11</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
